--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555832952</v>
+        <v>46157.93113960025</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113960025</v>
+        <v>46157.93137259544</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93137259544</v>
+        <v>46157.93384763946</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384763946</v>
+        <v>46157.9369644291</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369644291</v>
+        <v>46158.28205325254</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205325254</v>
+        <v>46158.29653267495</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653267495</v>
+        <v>46158.29808298674</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808298674</v>
+        <v>46158.33371133429</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371133429</v>
+        <v>46158.37222471715</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сентябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222471715</v>
+        <v>46158.37275997764</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
